--- a/Data/g10.2.xlsx
+++ b/Data/g10.2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         <v>2012</v>
       </c>
       <c r="B2" t="n">
-        <v>-3.379892373866011</v>
+        <v>-3.41585726704462</v>
       </c>
       <c r="C2" t="n">
-        <v>2.163515753146239</v>
+        <v>2.159927189314592</v>
       </c>
       <c r="D2" t="n">
-        <v>7.435808045749526</v>
+        <v>7.431438255623135</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2013</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2458231190647586</v>
+        <v>0.2673973987241451</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1875259260663009</v>
+        <v>-0.1502849307068899</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.007183601585049</v>
+        <v>-1.010828041581913</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>2014</v>
       </c>
       <c r="B4" t="n">
-        <v>5.627315197848137</v>
+        <v>5.632114905892083</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6384897485574692</v>
+        <v>0.6835650512782676</v>
       </c>
       <c r="D4" t="n">
-        <v>6.267274865596151</v>
+        <v>6.264894158674106</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>2015</v>
       </c>
       <c r="B5" t="n">
-        <v>6.179633245833416</v>
+        <v>6.174069398045412</v>
       </c>
       <c r="C5" t="n">
-        <v>-6.9249313127418</v>
+        <v>-6.975364497002778</v>
       </c>
       <c r="D5" t="n">
-        <v>9.755188628559864</v>
+        <v>9.753900026256401</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>2016</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.463003871040247</v>
+        <v>-1.516897204553513</v>
       </c>
       <c r="C6" t="n">
-        <v>-6.168894446832496</v>
+        <v>-6.158625398419016</v>
       </c>
       <c r="D6" t="n">
-        <v>8.007965298984665</v>
+        <v>8.007778796921228</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>2017</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.281383846374228</v>
+        <v>-0.2277549495745212</v>
       </c>
       <c r="C7" t="n">
-        <v>-4.930903865008629</v>
+        <v>-4.94998857578387</v>
       </c>
       <c r="D7" t="n">
-        <v>2.808051911452081</v>
+        <v>2.816557849061208</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>2018</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.9053869787370439</v>
+        <v>-0.9305432555286819</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.25472390457905</v>
+        <v>-4.282924108714569</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1299980927116806</v>
+        <v>0.1404805374504825</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>2019</v>
       </c>
       <c r="B9" t="n">
-        <v>4.664108877870277</v>
+        <v>4.727132503952003</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.162146239825368</v>
+        <v>-1.160282276562152</v>
       </c>
       <c r="D9" t="n">
-        <v>11.26357451946019</v>
+        <v>11.27635011116041</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>2020</v>
       </c>
       <c r="B10" t="n">
-        <v>-10.66327623651624</v>
+        <v>-10.6822233485994</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.589185233586303</v>
+        <v>-5.630180008561114</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.895858621317451</v>
+        <v>-5.89079401166932</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>2021</v>
       </c>
       <c r="B11" t="n">
-        <v>-6.406677988739851</v>
+        <v>-6.37680784889133</v>
       </c>
       <c r="C11" t="n">
-        <v>9.02352552360497</v>
+        <v>8.993388297474048</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.330421336695093</v>
+        <v>-7.285145335721833</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>2022</v>
       </c>
       <c r="B12" t="n">
-        <v>0.07376296021432971</v>
+        <v>0.01242515828436819</v>
       </c>
       <c r="C12" t="n">
-        <v>7.472375402118336</v>
+        <v>7.475491078582874</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.80355425882852</v>
+        <v>-10.77262323088896</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,27 @@
         <v>2023</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.493306323704991</v>
+        <v>-2.486392121955272</v>
       </c>
       <c r="C13" t="n">
-        <v>2.988660742308724</v>
+        <v>3.013949777500358</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.240237928329937</v>
+        <v>-3.186185580406364</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-2.952917057444504</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.526336479668624</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-3.216246793716948</v>
       </c>
     </row>
   </sheetData>
